--- a/Data/EC/NIT-9019715931.xlsx
+++ b/Data/EC/NIT-9019715931.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{715E3395-BE7E-4484-9EFA-D685FCE87D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C040875-47B3-4129-921A-8C754BC0FF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{67B64376-F12B-4BEA-AD3C-BAD45F63070B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4EBBE8D2-21AC-4EC7-BF6D-AD652B2E5B3A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -74,88 +74,115 @@
     <t>GUSTAVO JIMENEZ BOSIO</t>
   </si>
   <si>
+    <t>2607</t>
+  </si>
+  <si>
+    <t>1193049395</t>
+  </si>
+  <si>
+    <t>LAURA HELENA LONDOÑO HERRERA</t>
+  </si>
+  <si>
+    <t>1042581040</t>
+  </si>
+  <si>
+    <t>MATHEUS JAVIER MAZA PERTUZ</t>
+  </si>
+  <si>
+    <t>1143355474</t>
+  </si>
+  <si>
+    <t>JHANN CARLOS CASTILLO HUETO</t>
+  </si>
+  <si>
+    <t>PPT</t>
+  </si>
+  <si>
+    <t>1506959</t>
+  </si>
+  <si>
+    <t>ANGEL JOHAN SERRANO GIL</t>
+  </si>
+  <si>
+    <t>1100403039</t>
+  </si>
+  <si>
+    <t>JOSE GREGORIO AGUIRRE DE LA OSSA</t>
+  </si>
+  <si>
+    <t>1143409569</t>
+  </si>
+  <si>
+    <t>LAURA HERRERA GUZMAN</t>
+  </si>
+  <si>
+    <t>1143397870</t>
+  </si>
+  <si>
+    <t>AURA CRISTINA RODRIGUEZ DE HOYOS</t>
+  </si>
+  <si>
+    <t>1007960697</t>
+  </si>
+  <si>
+    <t>NESTOR MACHACON MEJIA</t>
+  </si>
+  <si>
+    <t>1143380458</t>
+  </si>
+  <si>
+    <t>DANIEL IVAN PEÑA GOMEZ</t>
+  </si>
+  <si>
+    <t>1235038652</t>
+  </si>
+  <si>
+    <t>ANGELI PAOLA ARANGO HINCAPIE</t>
+  </si>
+  <si>
+    <t>1143369866</t>
+  </si>
+  <si>
+    <t>DARILUZ ZUÑIGA GUZMAN</t>
+  </si>
+  <si>
+    <t>1048437110</t>
+  </si>
+  <si>
+    <t>CAMILA ANDREA CRUZ SERRANO</t>
+  </si>
+  <si>
+    <t>1002186292</t>
+  </si>
+  <si>
+    <t>GERARDO DE JESUS HERNANDEZ GARCIA</t>
+  </si>
+  <si>
+    <t>5900576</t>
+  </si>
+  <si>
+    <t>JUAN EDUARDO GONZALEZ CASTRO</t>
+  </si>
+  <si>
     <t>2606</t>
   </si>
   <si>
-    <t>1042581040</t>
-  </si>
-  <si>
-    <t>MATHEUS JAVIER MAZA PERTUZ</t>
-  </si>
-  <si>
-    <t>1143355474</t>
-  </si>
-  <si>
-    <t>JHANN CARLOS CASTILLO HUETO</t>
-  </si>
-  <si>
-    <t>PPT</t>
-  </si>
-  <si>
-    <t>1506959</t>
-  </si>
-  <si>
-    <t>ANGEL JOHAN SERRANO GIL</t>
-  </si>
-  <si>
-    <t>1100403039</t>
-  </si>
-  <si>
-    <t>JOSE GREGORIO AGUIRRE DE LA OSSA</t>
-  </si>
-  <si>
-    <t>1143409569</t>
-  </si>
-  <si>
-    <t>LAURA HERRERA GUZMAN</t>
-  </si>
-  <si>
-    <t>1143397870</t>
-  </si>
-  <si>
-    <t>AURA CRISTINA RODRIGUEZ DE HOYOS</t>
-  </si>
-  <si>
-    <t>1103496291</t>
-  </si>
-  <si>
-    <t>DANIELA LUCIA MENDOZA MANOTAS</t>
-  </si>
-  <si>
-    <t>1235038652</t>
-  </si>
-  <si>
-    <t>ANGELI PAOLA ARANGO HINCAPIE</t>
-  </si>
-  <si>
-    <t>1143369866</t>
-  </si>
-  <si>
-    <t>DARILUZ ZUÑIGA GUZMAN</t>
-  </si>
-  <si>
-    <t>1048437110</t>
-  </si>
-  <si>
-    <t>CAMILA ANDREA CRUZ SERRANO</t>
-  </si>
-  <si>
-    <t>1002186292</t>
-  </si>
-  <si>
-    <t>GERARDO DE JESUS HERNANDEZ GARCIA</t>
-  </si>
-  <si>
-    <t>1143398798</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO BRITO SALCEDO</t>
-  </si>
-  <si>
     <t>1002241827</t>
   </si>
   <si>
     <t>DYLAN JOSE MIER ARRIETA</t>
+  </si>
+  <si>
+    <t>1331826</t>
+  </si>
+  <si>
+    <t>SOL PIÃ±A</t>
+  </si>
+  <si>
+    <t>1143408751</t>
+  </si>
+  <si>
+    <t>RONALDO DE JESUS NAVAS MENDOZA</t>
   </si>
   <si>
     <t>1026300559</t>
@@ -560,22 +587,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FE5AF49-FA79-080F-F800-D396FE3328F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7D3F6A9-0B9A-CC1D-3F6C-2067F64B443A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -584,7 +611,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -597,7 +624,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -926,27 +953,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F04B429-52CC-4934-8A15-E46C20004CEC}">
-  <dimension ref="B2:J36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{928C7616-F1A8-4FE1-89DE-4C11996F85BB}">
+  <dimension ref="B2:J41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.86328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -955,7 +982,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -966,7 +993,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -977,7 +1004,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -988,10 +1015,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1004,8 +1031,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1020,15 +1047,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>1045886</v>
+        <v>1220463</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1036,27 +1063,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1076,16 +1103,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1108,7 +1135,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1122,7 +1149,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="18">
-        <v>70037</v>
+        <v>18676</v>
       </c>
       <c r="G17" s="18">
         <v>1750905</v>
@@ -1131,7 +1158,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1154,15 +1181,15 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="D19" s="17" t="s">
         <v>17</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>11</v>
@@ -1177,9 +1204,9 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>19</v>
@@ -1200,7 +1227,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1223,7 +1250,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1246,7 +1273,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1269,7 +1296,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1283,7 +1310,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="18">
-        <v>70037</v>
+        <v>18676</v>
       </c>
       <c r="G24" s="18">
         <v>1750905</v>
@@ -1292,7 +1319,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1306,7 +1333,7 @@
         <v>11</v>
       </c>
       <c r="F25" s="18">
-        <v>70037</v>
+        <v>18676</v>
       </c>
       <c r="G25" s="18">
         <v>1750905</v>
@@ -1315,7 +1342,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1338,7 +1365,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1361,7 +1388,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1384,7 +1411,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1407,57 +1434,172 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B30" s="21" t="s">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G30" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G31" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="24">
-        <v>65368</v>
-      </c>
-      <c r="G30" s="24">
-        <v>1750905</v>
-      </c>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B35" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="32"/>
-      <c r="H35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B36" s="32" t="s">
+      <c r="C32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G32" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G33" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G34" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="32"/>
-      <c r="H36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="E35" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="24">
+        <v>70037</v>
+      </c>
+      <c r="G35" s="24">
+        <v>1750905</v>
+      </c>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="26"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="32"/>
+      <c r="H40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="32"/>
+      <c r="H41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
